--- a/Till 4 Months.xlsx
+++ b/Till 4 Months.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981BE2D0-BDC5-4E46-AE7C-11D2CDA289C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988DA1C6-015A-4FB2-A8CC-2713E05EDBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="144">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -406,13 +406,67 @@
   </si>
   <si>
     <t>Chicken Chatkhara  (ECO) 60G</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Gm</t>
+  </si>
+  <si>
+    <t>TP Excl. GST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booker Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEM </t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>CHK</t>
+  </si>
+  <si>
+    <t>Zeshan</t>
+  </si>
+  <si>
+    <t>Salman Butt</t>
+  </si>
+  <si>
+    <t>Umair Rehman</t>
+  </si>
+  <si>
+    <t>Jabbar</t>
+  </si>
+  <si>
+    <t>Furqan</t>
+  </si>
+  <si>
+    <t>Shakoor Husain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nabeel Traders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdullah Traders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sohail Traders </t>
+  </si>
+  <si>
+    <t>Total Ctns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub Total </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,6 +506,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -479,7 +548,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -711,11 +780,351 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -771,6 +1180,33 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -783,32 +1219,149 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1127,7 +1680,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q118"/>
+  <dimension ref="A1:AJ118"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
@@ -1136,24 +1689,29 @@
     <col min="4" max="8" width="8.7265625" customWidth="1"/>
     <col min="9" max="9" width="9.36328125" customWidth="1"/>
     <col min="11" max="11" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5"/>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26"/>
-    </row>
-    <row r="2" spans="1:17" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
+    </row>
+    <row r="2" spans="1:36" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
@@ -1181,29 +1739,29 @@
       <c r="J2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="Q2" s="24" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1236,32 +1794,83 @@
       <c r="K3" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="25">
         <f>D3/40</f>
         <v>406.875</v>
       </c>
-      <c r="M3" s="29">
+      <c r="M3" s="25">
         <f>E3/40</f>
         <v>394.125</v>
       </c>
-      <c r="N3" s="29">
+      <c r="N3" s="25">
         <f>F3/40</f>
         <v>340.72500000000002</v>
       </c>
-      <c r="O3" s="29">
+      <c r="O3" s="25">
         <f>G3/40</f>
         <v>321.14999999999998</v>
       </c>
-      <c r="P3" s="29">
+      <c r="P3" s="25">
         <f>H3/40</f>
         <v>132.32499999999999</v>
       </c>
-      <c r="Q3" s="30">
+      <c r="Q3" s="26">
         <f>SUM(L3:P3)</f>
         <v>1595.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S3" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="T3" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="41">
+        <v>70</v>
+      </c>
+      <c r="V3" s="42">
+        <v>70</v>
+      </c>
+      <c r="W3" s="40">
+        <v>70</v>
+      </c>
+      <c r="X3" s="41">
+        <v>120</v>
+      </c>
+      <c r="Y3" s="42">
+        <v>120</v>
+      </c>
+      <c r="Z3" s="40">
+        <v>120</v>
+      </c>
+      <c r="AB3" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC3" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="64">
+        <v>70</v>
+      </c>
+      <c r="AE3" s="64">
+        <v>70</v>
+      </c>
+      <c r="AF3" s="64">
+        <v>70</v>
+      </c>
+      <c r="AG3" s="64">
+        <v>120</v>
+      </c>
+      <c r="AH3" s="64">
+        <v>120</v>
+      </c>
+      <c r="AI3" s="56">
+        <v>120</v>
+      </c>
+      <c r="AJ3" s="76" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
@@ -1294,32 +1903,77 @@
       <c r="K4" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="25">
         <f t="shared" ref="L4:L9" si="2">D4/40</f>
         <v>422.5</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="25">
         <f t="shared" ref="M4:M9" si="3">E4/40</f>
         <v>461.67500000000001</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="25">
         <f t="shared" ref="N4:N9" si="4">F4/40</f>
         <v>360.625</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="25">
         <f t="shared" ref="O4:O9" si="5">G4/40</f>
         <v>322.14999999999998</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="25">
         <f t="shared" ref="P4:P9" si="6">H4/40</f>
         <v>110.97499999999999</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="27">
         <f t="shared" ref="Q4:Q9" si="7">SUM(L4:P4)</f>
         <v>1677.9249999999997</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S4" s="43"/>
+      <c r="T4" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="U4" s="48">
+        <v>52.462499999999999</v>
+      </c>
+      <c r="V4" s="49">
+        <v>52.462499999999999</v>
+      </c>
+      <c r="W4" s="50">
+        <v>52.462499999999999</v>
+      </c>
+      <c r="X4" s="48">
+        <v>72.64</v>
+      </c>
+      <c r="Y4" s="49">
+        <v>72.64</v>
+      </c>
+      <c r="Z4" s="50">
+        <v>72.64</v>
+      </c>
+      <c r="AB4" s="81"/>
+      <c r="AC4" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD4" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE4" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF4" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG4" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH4" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI4" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ4" s="77"/>
+    </row>
+    <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
@@ -1352,32 +2006,63 @@
       <c r="K5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="L5" s="29">
+      <c r="L5" s="25">
         <f t="shared" si="2"/>
         <v>365.47500000000002</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="25">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="25">
         <f t="shared" si="4"/>
         <v>460.85</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="25">
         <f t="shared" si="5"/>
         <v>455.375</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="25">
         <f t="shared" si="6"/>
         <v>168.375</v>
       </c>
-      <c r="Q5" s="31">
+      <c r="Q5" s="27">
         <f t="shared" si="7"/>
         <v>1520.075</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S5" s="51"/>
+      <c r="T5" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="U5" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="V5" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="W5" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="X5" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y5" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z5" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB5" s="82"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="67"/>
+      <c r="AG5" s="67"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="69"/>
+      <c r="AJ5" s="78"/>
+    </row>
+    <row r="6" spans="1:36" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
         <v>5</v>
       </c>
@@ -1410,32 +2095,87 @@
       <c r="K6" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="25">
         <f t="shared" si="2"/>
         <v>626.20000000000005</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="25">
         <f t="shared" si="3"/>
         <v>769.85</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="25">
         <f t="shared" si="4"/>
         <v>688.97500000000002</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="25">
         <f t="shared" si="5"/>
         <v>592.95000000000005</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="25">
         <f t="shared" si="6"/>
         <v>287.35000000000002</v>
       </c>
-      <c r="Q6" s="31">
+      <c r="Q6" s="27">
         <f t="shared" si="7"/>
         <v>2965.3250000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T6" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="U6">
+        <v>683</v>
+      </c>
+      <c r="V6">
+        <v>647</v>
+      </c>
+      <c r="W6">
+        <v>1204</v>
+      </c>
+      <c r="X6">
+        <v>2296</v>
+      </c>
+      <c r="Y6">
+        <v>1622</v>
+      </c>
+      <c r="Z6">
+        <v>2686</v>
+      </c>
+      <c r="AB6" s="79">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD6" s="57">
+        <f>U6/40</f>
+        <v>17.074999999999999</v>
+      </c>
+      <c r="AE6" s="57">
+        <f>V6/40</f>
+        <v>16.175000000000001</v>
+      </c>
+      <c r="AF6" s="57">
+        <f>W6/40</f>
+        <v>30.1</v>
+      </c>
+      <c r="AG6" s="57">
+        <f>X6/40</f>
+        <v>57.4</v>
+      </c>
+      <c r="AH6" s="57">
+        <f>Y6/40</f>
+        <v>40.549999999999997</v>
+      </c>
+      <c r="AI6" s="57">
+        <f>Z6/40</f>
+        <v>67.150000000000006</v>
+      </c>
+      <c r="AJ6" s="62">
+        <f>SUM(AD6:AI6)</f>
+        <v>228.45000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
         <v>6</v>
       </c>
@@ -1468,32 +2208,87 @@
       <c r="K7" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="25">
         <f t="shared" si="2"/>
         <v>563.52499999999998</v>
       </c>
-      <c r="M7" s="29">
+      <c r="M7" s="25">
         <f t="shared" si="3"/>
         <v>634.5</v>
       </c>
-      <c r="N7" s="29">
+      <c r="N7" s="25">
         <f t="shared" si="4"/>
         <v>620.15</v>
       </c>
-      <c r="O7" s="29">
+      <c r="O7" s="25">
         <f t="shared" si="5"/>
         <v>550.54999999999995</v>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="25">
         <f t="shared" si="6"/>
         <v>256.85000000000002</v>
       </c>
-      <c r="Q7" s="31">
+      <c r="Q7" s="27">
         <f t="shared" si="7"/>
         <v>2625.5750000000003</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T7" s="54" t="s">
+        <v>134</v>
+      </c>
+      <c r="U7">
+        <v>720</v>
+      </c>
+      <c r="V7">
+        <v>564</v>
+      </c>
+      <c r="W7">
+        <v>744</v>
+      </c>
+      <c r="X7">
+        <v>1328</v>
+      </c>
+      <c r="Y7">
+        <v>964</v>
+      </c>
+      <c r="Z7">
+        <v>1337</v>
+      </c>
+      <c r="AB7" s="75">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD7" s="57">
+        <f t="shared" ref="AD7:AD14" si="8">U7/40</f>
+        <v>18</v>
+      </c>
+      <c r="AE7" s="57">
+        <f t="shared" ref="AE7:AE14" si="9">V7/40</f>
+        <v>14.1</v>
+      </c>
+      <c r="AF7" s="57">
+        <f t="shared" ref="AF7:AF14" si="10">W7/40</f>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AG7" s="57">
+        <f t="shared" ref="AG7:AG14" si="11">X7/40</f>
+        <v>33.200000000000003</v>
+      </c>
+      <c r="AH7" s="57">
+        <f t="shared" ref="AH7:AH14" si="12">Y7/40</f>
+        <v>24.1</v>
+      </c>
+      <c r="AI7" s="57">
+        <f t="shared" ref="AI7:AI14" si="13">Z7/40</f>
+        <v>33.424999999999997</v>
+      </c>
+      <c r="AJ7" s="59">
+        <f t="shared" ref="AJ7:AJ14" si="14">SUM(AD7:AI7)</f>
+        <v>141.42500000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
@@ -1526,32 +2321,87 @@
       <c r="K8" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="25">
         <f t="shared" si="2"/>
         <v>829.375</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="25">
         <f t="shared" si="3"/>
         <v>913.5</v>
       </c>
-      <c r="N8" s="29">
+      <c r="N8" s="25">
         <f t="shared" si="4"/>
         <v>935.57500000000005</v>
       </c>
-      <c r="O8" s="29">
+      <c r="O8" s="25">
         <f t="shared" si="5"/>
         <v>761.4</v>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="25">
         <f t="shared" si="6"/>
         <v>345.45</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="27">
         <f t="shared" si="7"/>
         <v>3785.2999999999997</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T8" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="U8">
+        <v>99</v>
+      </c>
+      <c r="V8">
+        <v>75</v>
+      </c>
+      <c r="W8">
+        <v>58</v>
+      </c>
+      <c r="X8">
+        <v>280</v>
+      </c>
+      <c r="Y8">
+        <v>263</v>
+      </c>
+      <c r="Z8">
+        <v>398</v>
+      </c>
+      <c r="AB8" s="75">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD8" s="57">
+        <f t="shared" si="8"/>
+        <v>2.4750000000000001</v>
+      </c>
+      <c r="AE8" s="57">
+        <f t="shared" si="9"/>
+        <v>1.875</v>
+      </c>
+      <c r="AF8" s="57">
+        <f t="shared" si="10"/>
+        <v>1.45</v>
+      </c>
+      <c r="AG8" s="57">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="AH8" s="57">
+        <f t="shared" si="12"/>
+        <v>6.5750000000000002</v>
+      </c>
+      <c r="AI8" s="57">
+        <f t="shared" si="13"/>
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="AJ8" s="59">
+        <f t="shared" si="14"/>
+        <v>29.324999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="13" t="s">
         <v>8</v>
       </c>
@@ -1582,58 +2432,113 @@
       <c r="K9" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="25">
         <f t="shared" si="2"/>
         <v>253.875</v>
       </c>
-      <c r="M9" s="29">
+      <c r="M9" s="25">
         <f t="shared" si="3"/>
         <v>801.77499999999998</v>
       </c>
-      <c r="N9" s="29">
+      <c r="N9" s="25">
         <f t="shared" si="4"/>
         <v>505.75</v>
       </c>
-      <c r="O9" s="29">
+      <c r="O9" s="25">
         <f t="shared" si="5"/>
         <v>217.8</v>
       </c>
-      <c r="P9" s="29">
+      <c r="P9" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="Q9" s="28">
         <f t="shared" si="7"/>
         <v>1779.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T9" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="U9">
+        <v>466</v>
+      </c>
+      <c r="V9">
+        <v>258</v>
+      </c>
+      <c r="W9">
+        <v>384</v>
+      </c>
+      <c r="X9">
+        <v>981</v>
+      </c>
+      <c r="Y9">
+        <v>705</v>
+      </c>
+      <c r="Z9">
+        <v>1065</v>
+      </c>
+      <c r="AB9" s="75">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="71" t="s">
+        <v>136</v>
+      </c>
+      <c r="AD9" s="57">
+        <f t="shared" si="8"/>
+        <v>11.65</v>
+      </c>
+      <c r="AE9" s="57">
+        <f t="shared" si="9"/>
+        <v>6.45</v>
+      </c>
+      <c r="AF9" s="57">
+        <f t="shared" si="10"/>
+        <v>9.6</v>
+      </c>
+      <c r="AG9" s="57">
+        <f t="shared" si="11"/>
+        <v>24.524999999999999</v>
+      </c>
+      <c r="AH9" s="57">
+        <f t="shared" si="12"/>
+        <v>17.625</v>
+      </c>
+      <c r="AI9" s="57">
+        <f t="shared" si="13"/>
+        <v>26.625</v>
+      </c>
+      <c r="AJ9" s="59">
+        <f t="shared" si="14"/>
+        <v>96.474999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="3">
-        <f t="shared" ref="D10:I10" si="8">SUM(D3:D9)</f>
+        <f t="shared" ref="D10:I10" si="15">SUM(D3:D9)</f>
         <v>138713</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>161817</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>156506</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>128855</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>52053</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>637944</v>
       </c>
       <c r="J10" s="22">
@@ -1641,32 +2546,87 @@
         <v>15948.6</v>
       </c>
       <c r="K10" s="8"/>
-      <c r="L10" s="33">
+      <c r="L10" s="29">
         <f>SUM(L3:L9)</f>
         <v>3467.8249999999998</v>
       </c>
-      <c r="M10" s="34">
-        <f t="shared" ref="M10:Q10" si="9">SUM(M3:M9)</f>
+      <c r="M10" s="30">
+        <f t="shared" ref="M10:Q10" si="16">SUM(M3:M9)</f>
         <v>4045.4250000000002</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="30">
+        <f t="shared" si="16"/>
+        <v>3912.6500000000005</v>
+      </c>
+      <c r="O10" s="30">
+        <f t="shared" si="16"/>
+        <v>3221.3750000000005</v>
+      </c>
+      <c r="P10" s="30">
+        <f t="shared" si="16"/>
+        <v>1301.325</v>
+      </c>
+      <c r="Q10" s="31">
+        <f t="shared" si="16"/>
+        <v>15948.6</v>
+      </c>
+      <c r="T10" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="U10">
+        <v>568</v>
+      </c>
+      <c r="V10">
+        <v>583</v>
+      </c>
+      <c r="W10">
+        <v>849</v>
+      </c>
+      <c r="X10">
+        <v>927</v>
+      </c>
+      <c r="Y10">
+        <v>682</v>
+      </c>
+      <c r="Z10">
+        <v>909</v>
+      </c>
+      <c r="AB10" s="75">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD10" s="57">
+        <f t="shared" si="8"/>
+        <v>14.2</v>
+      </c>
+      <c r="AE10" s="57">
         <f t="shared" si="9"/>
-        <v>3912.6500000000005</v>
-      </c>
-      <c r="O10" s="34">
-        <f t="shared" si="9"/>
-        <v>3221.3750000000005</v>
-      </c>
-      <c r="P10" s="34">
-        <f t="shared" si="9"/>
-        <v>1301.325</v>
-      </c>
-      <c r="Q10" s="35">
-        <f t="shared" si="9"/>
-        <v>15948.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>14.574999999999999</v>
+      </c>
+      <c r="AF10" s="57">
+        <f t="shared" si="10"/>
+        <v>21.225000000000001</v>
+      </c>
+      <c r="AG10" s="57">
+        <f t="shared" si="11"/>
+        <v>23.175000000000001</v>
+      </c>
+      <c r="AH10" s="57">
+        <f t="shared" si="12"/>
+        <v>17.05</v>
+      </c>
+      <c r="AI10" s="57">
+        <f t="shared" si="13"/>
+        <v>22.725000000000001</v>
+      </c>
+      <c r="AJ10" s="59">
+        <f t="shared" si="14"/>
+        <v>112.94999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
@@ -1692,24 +2652,134 @@
         <v>1301.325</v>
       </c>
       <c r="I11" s="17">
-        <f t="shared" ref="I11" si="10">I10/40</f>
+        <f t="shared" ref="I11" si="17">I10/40</f>
         <v>15948.6</v>
       </c>
       <c r="J11" s="19"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+      <c r="T11" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="U11">
+        <v>6378</v>
+      </c>
+      <c r="V11">
+        <v>6105</v>
+      </c>
+      <c r="W11">
+        <v>9249</v>
+      </c>
+      <c r="X11">
+        <v>10912</v>
+      </c>
+      <c r="Y11">
+        <v>11370</v>
+      </c>
+      <c r="Z11">
+        <v>16164</v>
+      </c>
+      <c r="AB11" s="75">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="71" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD11" s="57">
+        <f t="shared" si="8"/>
+        <v>159.44999999999999</v>
+      </c>
+      <c r="AE11" s="57">
+        <f t="shared" si="9"/>
+        <v>152.625</v>
+      </c>
+      <c r="AF11" s="57">
+        <f t="shared" si="10"/>
+        <v>231.22499999999999</v>
+      </c>
+      <c r="AG11" s="57">
+        <f t="shared" si="11"/>
+        <v>272.8</v>
+      </c>
+      <c r="AH11" s="57">
+        <f t="shared" si="12"/>
+        <v>284.25</v>
+      </c>
+      <c r="AI11" s="57">
+        <f t="shared" si="13"/>
+        <v>404.1</v>
+      </c>
+      <c r="AJ11" s="59">
+        <f t="shared" si="14"/>
+        <v>1504.4499999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T12" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="U12">
+        <v>800</v>
+      </c>
+      <c r="V12">
+        <v>200</v>
+      </c>
+      <c r="W12">
+        <v>200</v>
+      </c>
+      <c r="X12">
+        <v>5800</v>
+      </c>
+      <c r="Y12">
+        <v>4400</v>
+      </c>
+      <c r="Z12">
+        <v>5800</v>
+      </c>
+      <c r="AB12" s="75">
+        <v>7</v>
+      </c>
+      <c r="AC12" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="AD12" s="57">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="AE12" s="57">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="AF12" s="57">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="AG12" s="57">
+        <f t="shared" si="11"/>
+        <v>145</v>
+      </c>
+      <c r="AH12" s="57">
+        <f t="shared" si="12"/>
+        <v>110</v>
+      </c>
+      <c r="AI12" s="57">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="AJ12" s="59">
+        <f t="shared" si="14"/>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1726,8 +2796,63 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T13" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="U13">
+        <v>400</v>
+      </c>
+      <c r="V13">
+        <v>400</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>600</v>
+      </c>
+      <c r="Y13">
+        <v>800</v>
+      </c>
+      <c r="Z13">
+        <v>800</v>
+      </c>
+      <c r="AB13" s="75">
+        <v>8</v>
+      </c>
+      <c r="AC13" s="71" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD13" s="57">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="AE13" s="57">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="AF13" s="57">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="57">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="AH13" s="57">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="AI13" s="57">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="AJ13" s="59">
+        <f t="shared" si="14"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="4">
         <v>46239</v>
       </c>
@@ -1740,8 +2865,63 @@
       <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T14" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>600</v>
+      </c>
+      <c r="X14">
+        <v>800</v>
+      </c>
+      <c r="Y14">
+        <v>1200</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AB14" s="75">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="72" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD14" s="57">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE14" s="57">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="57">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="AG14" s="57">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="AH14" s="57">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="AI14" s="57">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="AJ14" s="60">
+        <f t="shared" si="14"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4">
         <v>46239</v>
       </c>
@@ -1754,8 +2934,40 @@
       <c r="D15" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="AB15" s="74"/>
+      <c r="AC15" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD15" s="58">
+        <f>SUM(AD6:AD14)</f>
+        <v>252.85</v>
+      </c>
+      <c r="AE15" s="58">
+        <f t="shared" ref="AE15:AJ15" si="18">SUM(AE6:AE14)</f>
+        <v>220.8</v>
+      </c>
+      <c r="AF15" s="58">
+        <f t="shared" si="18"/>
+        <v>332.2</v>
+      </c>
+      <c r="AG15" s="58">
+        <f t="shared" si="18"/>
+        <v>598.1</v>
+      </c>
+      <c r="AH15" s="58">
+        <f t="shared" si="18"/>
+        <v>550.15</v>
+      </c>
+      <c r="AI15" s="58">
+        <f t="shared" si="18"/>
+        <v>753.97500000000002</v>
+      </c>
+      <c r="AJ15" s="83">
+        <f t="shared" si="18"/>
+        <v>2708.0749999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>46240</v>
       </c>
@@ -1768,8 +2980,17 @@
       <c r="D16" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="L16" s="36"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="41"/>
+    </row>
+    <row r="17" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>46240</v>
       </c>
@@ -1782,8 +3003,17 @@
       <c r="D17" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="L17" s="43"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="50"/>
+      <c r="T17" s="48"/>
+    </row>
+    <row r="18" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>46240</v>
       </c>
@@ -1796,8 +3026,17 @@
       <c r="D18" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="L18" s="51"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="49"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="49"/>
+      <c r="S18" s="50"/>
+      <c r="T18" s="48"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>46240</v>
       </c>
@@ -1811,7 +3050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>46240</v>
       </c>
@@ -1825,7 +3064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>46241</v>
       </c>
@@ -1839,7 +3078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>46241</v>
       </c>
@@ -1853,7 +3092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>46242</v>
       </c>
@@ -1867,7 +3106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>46242</v>
       </c>
@@ -1881,7 +3120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>46242</v>
       </c>
@@ -1895,7 +3134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>46242</v>
       </c>
@@ -1909,7 +3148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>46242</v>
       </c>
@@ -1923,7 +3162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>46242</v>
       </c>
@@ -1937,7 +3176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>46244</v>
       </c>
@@ -1951,7 +3190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>46244</v>
       </c>
@@ -1965,7 +3204,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>46244</v>
       </c>
@@ -1979,7 +3218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>46244</v>
       </c>
@@ -3195,9 +4434,20 @@
       <c r="D118" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="13">
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AI4:AI5"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B1:J1"/>
+    <mergeCell ref="L16:L18"/>
+    <mergeCell ref="S3:S5"/>
+    <mergeCell ref="AB3:AB5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="44" orientation="portrait" r:id="rId1"/>

--- a/Till 4 Months.xlsx
+++ b/Till 4 Months.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988DA1C6-015A-4FB2-A8CC-2713E05EDBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A72F15F-EBA4-49CA-B084-CC586CC339C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -1207,18 +1207,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1240,9 +1228,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1264,9 +1249,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1294,31 +1276,10 @@
     <xf numFmtId="1" fontId="6" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="6" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1339,29 +1300,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1699,17 +1699,17 @@
   <sheetData>
     <row r="1" spans="1:36" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5"/>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="35"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="77"/>
     </row>
     <row r="2" spans="1:36" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="21" t="s">
@@ -1818,55 +1818,55 @@
         <f>SUM(L3:P3)</f>
         <v>1595.2</v>
       </c>
-      <c r="S3" s="36" t="s">
+      <c r="S3" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="T3" s="37" t="s">
+      <c r="T3" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="U3" s="41">
+      <c r="U3" s="37">
         <v>70</v>
       </c>
-      <c r="V3" s="42">
+      <c r="V3" s="38">
         <v>70</v>
       </c>
-      <c r="W3" s="40">
+      <c r="W3" s="36">
         <v>70</v>
       </c>
-      <c r="X3" s="41">
+      <c r="X3" s="37">
         <v>120</v>
       </c>
-      <c r="Y3" s="42">
+      <c r="Y3" s="38">
         <v>120</v>
       </c>
-      <c r="Z3" s="40">
+      <c r="Z3" s="36">
         <v>120</v>
       </c>
-      <c r="AB3" s="80" t="s">
+      <c r="AB3" s="81" t="s">
         <v>126</v>
       </c>
-      <c r="AC3" s="63" t="s">
+      <c r="AC3" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="AD3" s="64">
+      <c r="AD3" s="56">
         <v>70</v>
       </c>
-      <c r="AE3" s="64">
+      <c r="AE3" s="56">
         <v>70</v>
       </c>
-      <c r="AF3" s="64">
+      <c r="AF3" s="56">
         <v>70</v>
       </c>
-      <c r="AG3" s="64">
+      <c r="AG3" s="56">
         <v>120</v>
       </c>
-      <c r="AH3" s="64">
+      <c r="AH3" s="56">
         <v>120</v>
       </c>
-      <c r="AI3" s="56">
+      <c r="AI3" s="50">
         <v>120</v>
       </c>
-      <c r="AJ3" s="76" t="s">
+      <c r="AJ3" s="65" t="s">
         <v>142</v>
       </c>
     </row>
@@ -1927,51 +1927,51 @@
         <f t="shared" ref="Q4:Q9" si="7">SUM(L4:P4)</f>
         <v>1677.9249999999997</v>
       </c>
-      <c r="S4" s="43"/>
-      <c r="T4" s="44" t="s">
+      <c r="S4" s="79"/>
+      <c r="T4" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="U4" s="48">
+      <c r="U4" s="43">
         <v>52.462499999999999</v>
       </c>
-      <c r="V4" s="49">
+      <c r="V4" s="44">
         <v>52.462499999999999</v>
       </c>
-      <c r="W4" s="50">
+      <c r="W4" s="45">
         <v>52.462499999999999</v>
       </c>
-      <c r="X4" s="48">
+      <c r="X4" s="43">
         <v>72.64</v>
       </c>
-      <c r="Y4" s="49">
+      <c r="Y4" s="44">
         <v>72.64</v>
       </c>
-      <c r="Z4" s="50">
+      <c r="Z4" s="45">
         <v>72.64</v>
       </c>
-      <c r="AB4" s="81"/>
-      <c r="AC4" s="65" t="s">
+      <c r="AB4" s="82"/>
+      <c r="AC4" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="AD4" s="61" t="s">
+      <c r="AD4" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="AE4" s="61" t="s">
+      <c r="AE4" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="AF4" s="61" t="s">
+      <c r="AF4" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="AG4" s="61" t="s">
+      <c r="AG4" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="AH4" s="61" t="s">
+      <c r="AH4" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="AI4" s="68" t="s">
+      <c r="AI4" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="AJ4" s="77"/>
+      <c r="AJ4" s="66"/>
     </row>
     <row r="5" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="13" t="s">
@@ -2030,37 +2030,37 @@
         <f t="shared" si="7"/>
         <v>1520.075</v>
       </c>
-      <c r="S5" s="51"/>
-      <c r="T5" s="52" t="s">
+      <c r="S5" s="80"/>
+      <c r="T5" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="U5" s="48" t="s">
+      <c r="U5" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="V5" s="49" t="s">
+      <c r="V5" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="W5" s="50" t="s">
+      <c r="W5" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="X5" s="48" t="s">
+      <c r="X5" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="Y5" s="49" t="s">
+      <c r="Y5" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="Z5" s="50" t="s">
+      <c r="Z5" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="AB5" s="82"/>
-      <c r="AC5" s="66"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="67"/>
-      <c r="AG5" s="67"/>
-      <c r="AH5" s="67"/>
-      <c r="AI5" s="69"/>
-      <c r="AJ5" s="78"/>
+      <c r="AB5" s="83"/>
+      <c r="AC5" s="69"/>
+      <c r="AD5" s="71"/>
+      <c r="AE5" s="71"/>
+      <c r="AF5" s="71"/>
+      <c r="AG5" s="71"/>
+      <c r="AH5" s="71"/>
+      <c r="AI5" s="73"/>
+      <c r="AJ5" s="67"/>
     </row>
     <row r="6" spans="1:36" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
@@ -2119,7 +2119,7 @@
         <f t="shared" si="7"/>
         <v>2965.3250000000003</v>
       </c>
-      <c r="T6" s="54" t="s">
+      <c r="T6" s="48" t="s">
         <v>133</v>
       </c>
       <c r="U6">
@@ -2140,37 +2140,37 @@
       <c r="Z6">
         <v>2686</v>
       </c>
-      <c r="AB6" s="79">
+      <c r="AB6" s="63">
         <v>1</v>
       </c>
-      <c r="AC6" s="70" t="s">
+      <c r="AC6" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="AD6" s="57">
-        <f>U6/40</f>
+      <c r="AD6" s="51">
+        <f t="shared" ref="AD6:AI6" si="8">U6/40</f>
         <v>17.074999999999999</v>
       </c>
-      <c r="AE6" s="57">
-        <f>V6/40</f>
+      <c r="AE6" s="51">
+        <f t="shared" si="8"/>
         <v>16.175000000000001</v>
       </c>
-      <c r="AF6" s="57">
-        <f>W6/40</f>
+      <c r="AF6" s="51">
+        <f t="shared" si="8"/>
         <v>30.1</v>
       </c>
-      <c r="AG6" s="57">
-        <f>X6/40</f>
+      <c r="AG6" s="51">
+        <f t="shared" si="8"/>
         <v>57.4</v>
       </c>
-      <c r="AH6" s="57">
-        <f>Y6/40</f>
+      <c r="AH6" s="51">
+        <f t="shared" si="8"/>
         <v>40.549999999999997</v>
       </c>
-      <c r="AI6" s="57">
-        <f>Z6/40</f>
+      <c r="AI6" s="51">
+        <f t="shared" si="8"/>
         <v>67.150000000000006</v>
       </c>
-      <c r="AJ6" s="62">
+      <c r="AJ6" s="55">
         <f>SUM(AD6:AI6)</f>
         <v>228.45000000000002</v>
       </c>
@@ -2232,7 +2232,7 @@
         <f t="shared" si="7"/>
         <v>2625.5750000000003</v>
       </c>
-      <c r="T7" s="54" t="s">
+      <c r="T7" s="48" t="s">
         <v>134</v>
       </c>
       <c r="U7">
@@ -2253,38 +2253,38 @@
       <c r="Z7">
         <v>1337</v>
       </c>
-      <c r="AB7" s="75">
+      <c r="AB7" s="62">
         <v>2</v>
       </c>
-      <c r="AC7" s="71" t="s">
+      <c r="AC7" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="57">
-        <f t="shared" ref="AD7:AD14" si="8">U7/40</f>
-        <v>18</v>
-      </c>
-      <c r="AE7" s="57">
-        <f t="shared" ref="AE7:AE14" si="9">V7/40</f>
+      <c r="AD7" s="51">
+        <f t="shared" ref="AD7:AD14" si="9">U7/40</f>
+        <v>18</v>
+      </c>
+      <c r="AE7" s="51">
+        <f t="shared" ref="AE7:AE14" si="10">V7/40</f>
         <v>14.1</v>
       </c>
-      <c r="AF7" s="57">
-        <f t="shared" ref="AF7:AF14" si="10">W7/40</f>
+      <c r="AF7" s="51">
+        <f t="shared" ref="AF7:AF14" si="11">W7/40</f>
         <v>18.600000000000001</v>
       </c>
-      <c r="AG7" s="57">
-        <f t="shared" ref="AG7:AG14" si="11">X7/40</f>
+      <c r="AG7" s="51">
+        <f t="shared" ref="AG7:AG14" si="12">X7/40</f>
         <v>33.200000000000003</v>
       </c>
-      <c r="AH7" s="57">
-        <f t="shared" ref="AH7:AH14" si="12">Y7/40</f>
+      <c r="AH7" s="51">
+        <f t="shared" ref="AH7:AH14" si="13">Y7/40</f>
         <v>24.1</v>
       </c>
-      <c r="AI7" s="57">
-        <f t="shared" ref="AI7:AI14" si="13">Z7/40</f>
+      <c r="AI7" s="51">
+        <f t="shared" ref="AI7:AI14" si="14">Z7/40</f>
         <v>33.424999999999997</v>
       </c>
-      <c r="AJ7" s="59">
-        <f t="shared" ref="AJ7:AJ14" si="14">SUM(AD7:AI7)</f>
+      <c r="AJ7" s="53">
+        <f t="shared" ref="AJ7:AJ14" si="15">SUM(AD7:AI7)</f>
         <v>141.42500000000001</v>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
         <f t="shared" si="7"/>
         <v>3785.2999999999997</v>
       </c>
-      <c r="T8" s="54" t="s">
+      <c r="T8" s="48" t="s">
         <v>135</v>
       </c>
       <c r="U8">
@@ -2366,38 +2366,38 @@
       <c r="Z8">
         <v>398</v>
       </c>
-      <c r="AB8" s="75">
+      <c r="AB8" s="62">
         <v>3</v>
       </c>
-      <c r="AC8" s="71" t="s">
+      <c r="AC8" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="AD8" s="57">
-        <f t="shared" si="8"/>
+      <c r="AD8" s="51">
+        <f t="shared" si="9"/>
         <v>2.4750000000000001</v>
       </c>
-      <c r="AE8" s="57">
-        <f t="shared" si="9"/>
+      <c r="AE8" s="51">
+        <f t="shared" si="10"/>
         <v>1.875</v>
       </c>
-      <c r="AF8" s="57">
-        <f t="shared" si="10"/>
+      <c r="AF8" s="51">
+        <f t="shared" si="11"/>
         <v>1.45</v>
       </c>
-      <c r="AG8" s="57">
-        <f t="shared" si="11"/>
+      <c r="AG8" s="51">
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="AH8" s="57">
-        <f t="shared" si="12"/>
+      <c r="AH8" s="51">
+        <f t="shared" si="13"/>
         <v>6.5750000000000002</v>
       </c>
-      <c r="AI8" s="57">
-        <f t="shared" si="13"/>
+      <c r="AI8" s="51">
+        <f t="shared" si="14"/>
         <v>9.9499999999999993</v>
       </c>
-      <c r="AJ8" s="59">
-        <f t="shared" si="14"/>
+      <c r="AJ8" s="53">
+        <f t="shared" si="15"/>
         <v>29.324999999999999</v>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
         <f t="shared" si="7"/>
         <v>1779.2</v>
       </c>
-      <c r="T9" s="54" t="s">
+      <c r="T9" s="48" t="s">
         <v>136</v>
       </c>
       <c r="U9">
@@ -2477,38 +2477,38 @@
       <c r="Z9">
         <v>1065</v>
       </c>
-      <c r="AB9" s="75">
+      <c r="AB9" s="62">
         <v>4</v>
       </c>
-      <c r="AC9" s="71" t="s">
+      <c r="AC9" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="AD9" s="57">
-        <f t="shared" si="8"/>
+      <c r="AD9" s="51">
+        <f t="shared" si="9"/>
         <v>11.65</v>
       </c>
-      <c r="AE9" s="57">
-        <f t="shared" si="9"/>
+      <c r="AE9" s="51">
+        <f t="shared" si="10"/>
         <v>6.45</v>
       </c>
-      <c r="AF9" s="57">
-        <f t="shared" si="10"/>
+      <c r="AF9" s="51">
+        <f t="shared" si="11"/>
         <v>9.6</v>
       </c>
-      <c r="AG9" s="57">
-        <f t="shared" si="11"/>
+      <c r="AG9" s="51">
+        <f t="shared" si="12"/>
         <v>24.524999999999999</v>
       </c>
-      <c r="AH9" s="57">
-        <f t="shared" si="12"/>
+      <c r="AH9" s="51">
+        <f t="shared" si="13"/>
         <v>17.625</v>
       </c>
-      <c r="AI9" s="57">
-        <f t="shared" si="13"/>
+      <c r="AI9" s="51">
+        <f t="shared" si="14"/>
         <v>26.625</v>
       </c>
-      <c r="AJ9" s="59">
-        <f t="shared" si="14"/>
+      <c r="AJ9" s="53">
+        <f t="shared" si="15"/>
         <v>96.474999999999994</v>
       </c>
     </row>
@@ -2518,27 +2518,27 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="3">
-        <f t="shared" ref="D10:I10" si="15">SUM(D3:D9)</f>
+        <f t="shared" ref="D10:I10" si="16">SUM(D3:D9)</f>
         <v>138713</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>161817</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>156506</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>128855</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>52053</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>637944</v>
       </c>
       <c r="J10" s="22">
@@ -2551,26 +2551,26 @@
         <v>3467.8249999999998</v>
       </c>
       <c r="M10" s="30">
-        <f t="shared" ref="M10:Q10" si="16">SUM(M3:M9)</f>
+        <f t="shared" ref="M10:Q10" si="17">SUM(M3:M9)</f>
         <v>4045.4250000000002</v>
       </c>
       <c r="N10" s="30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3912.6500000000005</v>
       </c>
       <c r="O10" s="30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3221.3750000000005</v>
       </c>
       <c r="P10" s="30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1301.325</v>
       </c>
       <c r="Q10" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>15948.6</v>
       </c>
-      <c r="T10" s="54" t="s">
+      <c r="T10" s="48" t="s">
         <v>137</v>
       </c>
       <c r="U10">
@@ -2591,38 +2591,38 @@
       <c r="Z10">
         <v>909</v>
       </c>
-      <c r="AB10" s="75">
+      <c r="AB10" s="62">
         <v>5</v>
       </c>
-      <c r="AC10" s="71" t="s">
+      <c r="AC10" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="AD10" s="57">
-        <f t="shared" si="8"/>
+      <c r="AD10" s="51">
+        <f t="shared" si="9"/>
         <v>14.2</v>
       </c>
-      <c r="AE10" s="57">
-        <f t="shared" si="9"/>
+      <c r="AE10" s="51">
+        <f t="shared" si="10"/>
         <v>14.574999999999999</v>
       </c>
-      <c r="AF10" s="57">
-        <f t="shared" si="10"/>
+      <c r="AF10" s="51">
+        <f t="shared" si="11"/>
         <v>21.225000000000001</v>
       </c>
-      <c r="AG10" s="57">
-        <f t="shared" si="11"/>
+      <c r="AG10" s="51">
+        <f t="shared" si="12"/>
         <v>23.175000000000001</v>
       </c>
-      <c r="AH10" s="57">
-        <f t="shared" si="12"/>
+      <c r="AH10" s="51">
+        <f t="shared" si="13"/>
         <v>17.05</v>
       </c>
-      <c r="AI10" s="57">
-        <f t="shared" si="13"/>
+      <c r="AI10" s="51">
+        <f t="shared" si="14"/>
         <v>22.725000000000001</v>
       </c>
-      <c r="AJ10" s="59">
-        <f t="shared" si="14"/>
+      <c r="AJ10" s="53">
+        <f t="shared" si="15"/>
         <v>112.94999999999999</v>
       </c>
     </row>
@@ -2652,11 +2652,11 @@
         <v>1301.325</v>
       </c>
       <c r="I11" s="17">
-        <f t="shared" ref="I11" si="17">I10/40</f>
+        <f t="shared" ref="I11" si="18">I10/40</f>
         <v>15948.6</v>
       </c>
       <c r="J11" s="19"/>
-      <c r="T11" s="54" t="s">
+      <c r="T11" s="48" t="s">
         <v>138</v>
       </c>
       <c r="U11">
@@ -2677,53 +2677,53 @@
       <c r="Z11">
         <v>16164</v>
       </c>
-      <c r="AB11" s="75">
+      <c r="AB11" s="62">
         <v>6</v>
       </c>
-      <c r="AC11" s="71" t="s">
+      <c r="AC11" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="AD11" s="57">
-        <f t="shared" si="8"/>
+      <c r="AD11" s="51">
+        <f t="shared" si="9"/>
         <v>159.44999999999999</v>
       </c>
-      <c r="AE11" s="57">
-        <f t="shared" si="9"/>
+      <c r="AE11" s="51">
+        <f t="shared" si="10"/>
         <v>152.625</v>
       </c>
-      <c r="AF11" s="57">
-        <f t="shared" si="10"/>
+      <c r="AF11" s="51">
+        <f t="shared" si="11"/>
         <v>231.22499999999999</v>
       </c>
-      <c r="AG11" s="57">
-        <f t="shared" si="11"/>
+      <c r="AG11" s="51">
+        <f t="shared" si="12"/>
         <v>272.8</v>
       </c>
-      <c r="AH11" s="57">
-        <f t="shared" si="12"/>
+      <c r="AH11" s="51">
+        <f t="shared" si="13"/>
         <v>284.25</v>
       </c>
-      <c r="AI11" s="57">
-        <f t="shared" si="13"/>
+      <c r="AI11" s="51">
+        <f t="shared" si="14"/>
         <v>404.1</v>
       </c>
-      <c r="AJ11" s="59">
-        <f t="shared" si="14"/>
+      <c r="AJ11" s="53">
+        <f t="shared" si="15"/>
         <v>1504.4499999999998</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="T12" s="54" t="s">
+      <c r="T12" s="48" t="s">
         <v>139</v>
       </c>
       <c r="U12">
@@ -2744,38 +2744,38 @@
       <c r="Z12">
         <v>5800</v>
       </c>
-      <c r="AB12" s="75">
+      <c r="AB12" s="62">
         <v>7</v>
       </c>
-      <c r="AC12" s="71" t="s">
+      <c r="AC12" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="AD12" s="57">
-        <f t="shared" si="8"/>
+      <c r="AD12" s="51">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="AE12" s="57">
-        <f t="shared" si="9"/>
-        <v>5</v>
-      </c>
-      <c r="AF12" s="57">
+      <c r="AE12" s="51">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="AG12" s="57">
+      <c r="AF12" s="51">
         <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="AG12" s="51">
+        <f t="shared" si="12"/>
         <v>145</v>
       </c>
-      <c r="AH12" s="57">
-        <f t="shared" si="12"/>
+      <c r="AH12" s="51">
+        <f t="shared" si="13"/>
         <v>110</v>
       </c>
-      <c r="AI12" s="57">
-        <f t="shared" si="13"/>
+      <c r="AI12" s="51">
+        <f t="shared" si="14"/>
         <v>145</v>
       </c>
-      <c r="AJ12" s="59">
-        <f t="shared" si="14"/>
+      <c r="AJ12" s="53">
+        <f t="shared" si="15"/>
         <v>430</v>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="T13" s="55" t="s">
+      <c r="T13" s="49" t="s">
         <v>140</v>
       </c>
       <c r="U13">
@@ -2817,38 +2817,38 @@
       <c r="Z13">
         <v>800</v>
       </c>
-      <c r="AB13" s="75">
+      <c r="AB13" s="62">
         <v>8</v>
       </c>
-      <c r="AC13" s="71" t="s">
+      <c r="AC13" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="AD13" s="57">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="AE13" s="57">
+      <c r="AD13" s="51">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="AF13" s="57">
+      <c r="AE13" s="51">
         <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="AF13" s="51">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AG13" s="57">
-        <f t="shared" si="11"/>
+      <c r="AG13" s="51">
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="AH13" s="57">
-        <f t="shared" si="12"/>
-        <v>20</v>
-      </c>
-      <c r="AI13" s="57">
+      <c r="AH13" s="51">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="AJ13" s="59">
+      <c r="AI13" s="51">
         <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="AJ13" s="53">
+        <f t="shared" si="15"/>
         <v>75</v>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T14" s="55" t="s">
+      <c r="T14" s="49" t="s">
         <v>141</v>
       </c>
       <c r="U14">
@@ -2886,38 +2886,38 @@
       <c r="Z14">
         <v>1000</v>
       </c>
-      <c r="AB14" s="75">
+      <c r="AB14" s="62">
         <v>9</v>
       </c>
-      <c r="AC14" s="72" t="s">
+      <c r="AC14" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="AD14" s="57">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AE14" s="57">
+      <c r="AD14" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="57">
+      <c r="AE14" s="51">
         <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="51">
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="AG14" s="57">
-        <f t="shared" si="11"/>
+      <c r="AG14" s="51">
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="AH14" s="57">
-        <f t="shared" si="12"/>
+      <c r="AH14" s="51">
+        <f t="shared" si="13"/>
         <v>30</v>
       </c>
-      <c r="AI14" s="57">
-        <f t="shared" si="13"/>
+      <c r="AI14" s="51">
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="AJ14" s="60">
-        <f t="shared" si="14"/>
+      <c r="AJ14" s="54">
+        <f t="shared" si="15"/>
         <v>90</v>
       </c>
     </row>
@@ -2934,36 +2934,36 @@
       <c r="D15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AB15" s="74"/>
-      <c r="AC15" s="73" t="s">
+      <c r="AB15" s="61"/>
+      <c r="AC15" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="AD15" s="58">
+      <c r="AD15" s="52">
         <f>SUM(AD6:AD14)</f>
         <v>252.85</v>
       </c>
-      <c r="AE15" s="58">
-        <f t="shared" ref="AE15:AJ15" si="18">SUM(AE6:AE14)</f>
+      <c r="AE15" s="52">
+        <f t="shared" ref="AE15:AJ15" si="19">SUM(AE6:AE14)</f>
         <v>220.8</v>
       </c>
-      <c r="AF15" s="58">
-        <f t="shared" si="18"/>
+      <c r="AF15" s="52">
+        <f t="shared" si="19"/>
         <v>332.2</v>
       </c>
-      <c r="AG15" s="58">
-        <f t="shared" si="18"/>
+      <c r="AG15" s="52">
+        <f t="shared" si="19"/>
         <v>598.1</v>
       </c>
-      <c r="AH15" s="58">
-        <f t="shared" si="18"/>
+      <c r="AH15" s="52">
+        <f t="shared" si="19"/>
         <v>550.15</v>
       </c>
-      <c r="AI15" s="58">
-        <f t="shared" si="18"/>
+      <c r="AI15" s="52">
+        <f t="shared" si="19"/>
         <v>753.97500000000002</v>
       </c>
-      <c r="AJ15" s="83">
-        <f t="shared" si="18"/>
+      <c r="AJ15" s="64">
+        <f t="shared" si="19"/>
         <v>2708.0749999999998</v>
       </c>
     </row>
@@ -2980,15 +2980,15 @@
       <c r="D16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L16" s="36"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="41"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="37"/>
     </row>
     <row r="17" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
@@ -3003,15 +3003,15 @@
       <c r="D17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="43"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="50"/>
-      <c r="T17" s="48"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="43"/>
     </row>
     <row r="18" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
@@ -3026,15 +3026,15 @@
       <c r="D18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L18" s="51"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="49"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="49"/>
-      <c r="S18" s="50"/>
-      <c r="T18" s="48"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="43"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
@@ -4435,6 +4435,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="L16:L18"/>
+    <mergeCell ref="S3:S5"/>
+    <mergeCell ref="AB3:AB5"/>
     <mergeCell ref="AJ3:AJ5"/>
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -4443,11 +4448,6 @@
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="L16:L18"/>
-    <mergeCell ref="S3:S5"/>
-    <mergeCell ref="AB3:AB5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="44" orientation="portrait" r:id="rId1"/>
